--- a/Data/data_by_6_cyl.xlsx
+++ b/Data/data_by_6_cyl.xlsx
@@ -13,6 +13,44 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="11">
+  <si>
+    <t>mpg</t>
+  </si>
+  <si>
+    <t>cyl</t>
+  </si>
+  <si>
+    <t>disp</t>
+  </si>
+  <si>
+    <t>hp</t>
+  </si>
+  <si>
+    <t>drat</t>
+  </si>
+  <si>
+    <t>wt</t>
+  </si>
+  <si>
+    <t>qsec</t>
+  </si>
+  <si>
+    <t>vs</t>
+  </si>
+  <si>
+    <t>am</t>
+  </si>
+  <si>
+    <t>gear</t>
+  </si>
+  <si>
+    <t>carb</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -356,64 +394,42 @@
   <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>mpg</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>cyl</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>disp</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>hp</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>drat</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>wt</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>qsec</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>am</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>gear</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>carb</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:11" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>21.4</v>
       </c>
@@ -448,7 +464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>18.1</v>
       </c>
@@ -493,64 +509,42 @@
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>mpg</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>cyl</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>disp</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>hp</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>drat</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>wt</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>qsec</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>am</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>gear</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>carb</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:11" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>21</v>
       </c>
@@ -585,7 +579,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>21</v>
       </c>
@@ -620,7 +614,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>19.2</v>
       </c>
@@ -655,7 +649,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>17.8</v>
       </c>
@@ -700,64 +694,42 @@
   <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>mpg</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>cyl</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>disp</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>hp</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>drat</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>wt</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>qsec</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>am</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>gear</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>carb</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:11" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>19.7</v>
       </c>
